--- a/tass-converter/tests/data/simple_demo.xlsx
+++ b/tass-converter/tests/data/simple_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desjajo\Documents\_Python\tass-ssat\tass-converter\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747449BA-8A1C-40F6-BBB3-5494EB421996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C6082D-AE44-47E6-8E3F-A6BFE085386C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tr0001" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="chrome001" sheetId="5" r:id="rId5"/>
     <sheet name="chrome002" sheetId="6" r:id="rId6"/>
     <sheet name="ffox001" sheetId="7" r:id="rId7"/>
-    <sheet name="ffox002" sheetId="8" r:id="rId8"/>
+    <sheet name="android" sheetId="8" r:id="rId8"/>
+    <sheet name="ffox002" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="100">
   <si>
     <t>tr_uuid:</t>
   </si>
@@ -70,30 +71,30 @@
     <t>reporters:</t>
   </si>
   <si>
+    <t>drivers:</t>
+  </si>
+  <si>
+    <t>chrome001</t>
+  </si>
+  <si>
+    <t>others:</t>
+  </si>
+  <si>
+    <t>Uuid-tc-02</t>
+  </si>
+  <si>
+    <t>ffox002</t>
+  </si>
+  <si>
+    <t>android001</t>
+  </si>
+  <si>
+    <t>tr2</t>
+  </si>
+  <si>
     <t>browsers:</t>
   </si>
   <si>
-    <t>chrome001</t>
-  </si>
-  <si>
-    <t>others:</t>
-  </si>
-  <si>
-    <t>testrail</t>
-  </si>
-  <si>
-    <t>Uuid-tc-02</t>
-  </si>
-  <si>
-    <t>ffox002</t>
-  </si>
-  <si>
-    <t>project_id,321</t>
-  </si>
-  <si>
-    <t>tr2</t>
-  </si>
-  <si>
     <t>chrome002</t>
   </si>
   <si>
@@ -136,6 +137,177 @@
     <t>soft</t>
   </si>
   <si>
+    <t>q1</t>
+  </si>
+  <si>
+    <t>Launch test page</t>
+  </si>
+  <si>
+    <t>selenium,load_file</t>
+  </si>
+  <si>
+    <t>examples/demo-html/page1.html</t>
+  </si>
+  <si>
+    <t>q2</t>
+  </si>
+  <si>
+    <t>Assert page is open</t>
+  </si>
+  <si>
+    <t>selenium,assert_page_is_open</t>
+  </si>
+  <si>
+    <t>sample,page1</t>
+  </si>
+  <si>
+    <t>q3</t>
+  </si>
+  <si>
+    <t>Wait for element then type</t>
+  </si>
+  <si>
+    <t>selwait,wait_element_visible</t>
+  </si>
+  <si>
+    <t>id,nameField</t>
+  </si>
+  <si>
+    <t>selenium,write</t>
+  </si>
+  <si>
+    <t>do a barrel roll</t>
+  </si>
+  <si>
+    <t>q4</t>
+  </si>
+  <si>
+    <t>Click a button</t>
+  </si>
+  <si>
+    <t>selenium,click</t>
+  </si>
+  <si>
+    <t>btnColor</t>
+  </si>
+  <si>
+    <t>q5</t>
+  </si>
+  <si>
+    <t>Read CSS</t>
+  </si>
+  <si>
+    <t>selenium,read_css</t>
+  </si>
+  <si>
+    <t>background-color</t>
+  </si>
+  <si>
+    <t>q6</t>
+  </si>
+  <si>
+    <t>Assert element is displayed</t>
+  </si>
+  <si>
+    <t>selenium,assert_displayed</t>
+  </si>
+  <si>
+    <t>btnX</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>q7</t>
+  </si>
+  <si>
+    <t>q8</t>
+  </si>
+  <si>
+    <t>Tass Sample Case B</t>
+  </si>
+  <si>
+    <t>locator_args</t>
+  </si>
+  <si>
+    <t>q6a</t>
+  </si>
+  <si>
+    <t>btnFormat</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>br_uuid:</t>
+  </si>
+  <si>
+    <t>browser_name:</t>
+  </si>
+  <si>
+    <t>chrome</t>
+  </si>
+  <si>
+    <t>key,value</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>driver:</t>
+  </si>
+  <si>
+    <t>implicit_wait,5</t>
+  </si>
+  <si>
+    <t>browser_arguments:</t>
+  </si>
+  <si>
+    <t>--start-maximized</t>
+  </si>
+  <si>
+    <t>browser_preferences:</t>
+  </si>
+  <si>
+    <t>explicit_wait,10</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>--headless</t>
+  </si>
+  <si>
+    <t>firefox</t>
+  </si>
+  <si>
+    <t>implicit_wait,15</t>
+  </si>
+  <si>
+    <t>explicit_wait,30</t>
+  </si>
+  <si>
+    <t>mb_uuid:</t>
+  </si>
+  <si>
+    <t>platform_name:</t>
+  </si>
+  <si>
+    <t>android</t>
+  </si>
+  <si>
+    <t>key[,value]</t>
+  </si>
+  <si>
+    <t>appium:</t>
+  </si>
+  <si>
+    <t>--testing1</t>
+  </si>
+  <si>
+    <t>--testing,more</t>
+  </si>
+  <si>
     <t>target</t>
   </si>
   <si>
@@ -145,93 +317,6 @@
     <t>delta</t>
   </si>
   <si>
-    <t>q1</t>
-  </si>
-  <si>
-    <t>Launch test page</t>
-  </si>
-  <si>
-    <t>selenium,load_file</t>
-  </si>
-  <si>
-    <t>examples/demo-html/page1.html</t>
-  </si>
-  <si>
-    <t>q2</t>
-  </si>
-  <si>
-    <t>Assert page is open</t>
-  </si>
-  <si>
-    <t>selenium,assert_page_is_open</t>
-  </si>
-  <si>
-    <t>sample,page1</t>
-  </si>
-  <si>
-    <t>q3</t>
-  </si>
-  <si>
-    <t>Wait for element then type</t>
-  </si>
-  <si>
-    <t>selwait,wait_element_visible</t>
-  </si>
-  <si>
-    <t>id,nameField</t>
-  </si>
-  <si>
-    <t>selenium,write</t>
-  </si>
-  <si>
-    <t>do a barrel roll</t>
-  </si>
-  <si>
-    <t>q4</t>
-  </si>
-  <si>
-    <t>Click a button</t>
-  </si>
-  <si>
-    <t>selenium,click</t>
-  </si>
-  <si>
-    <t>btnColor</t>
-  </si>
-  <si>
-    <t>q5</t>
-  </si>
-  <si>
-    <t>Read CSS</t>
-  </si>
-  <si>
-    <t>selenium,read_css</t>
-  </si>
-  <si>
-    <t>background-color</t>
-  </si>
-  <si>
-    <t>q6</t>
-  </si>
-  <si>
-    <t>Assert element is displayed</t>
-  </si>
-  <si>
-    <t>selenium,assert_displayed</t>
-  </si>
-  <si>
-    <t>btnX</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>q7</t>
-  </si>
-  <si>
-    <t>q8</t>
-  </si>
-  <si>
     <t>q9</t>
   </si>
   <si>
@@ -248,69 +333,6 @@
   </si>
   <si>
     <t>100,90</t>
-  </si>
-  <si>
-    <t>Tass Sample Case B</t>
-  </si>
-  <si>
-    <t>locator_args</t>
-  </si>
-  <si>
-    <t>q6a</t>
-  </si>
-  <si>
-    <t>btnFormat</t>
-  </si>
-  <si>
-    <t>Color</t>
-  </si>
-  <si>
-    <t>br_uuid:</t>
-  </si>
-  <si>
-    <t>browser_name:</t>
-  </si>
-  <si>
-    <t>chrome</t>
-  </si>
-  <si>
-    <t>key,value</t>
-  </si>
-  <si>
-    <t>flag</t>
-  </si>
-  <si>
-    <t>driver:</t>
-  </si>
-  <si>
-    <t>implicit_wait,5</t>
-  </si>
-  <si>
-    <t>browser_arguments:</t>
-  </si>
-  <si>
-    <t>--start-maximized</t>
-  </si>
-  <si>
-    <t>browser_preferences:</t>
-  </si>
-  <si>
-    <t>explicit_wait,10</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>--headless</t>
-  </si>
-  <si>
-    <t>firefox</t>
-  </si>
-  <si>
-    <t>implicit_wait,15</t>
-  </si>
-  <si>
-    <t>explicit_wait,30</t>
   </si>
 </sst>
 </file>
@@ -351,11 +373,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -619,24 +638,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="11.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="11.7109375" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -650,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -672,19 +691,18 @@
       <c r="I3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
         <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -699,24 +717,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="11.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="11.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
+      <c r="B1" t="s">
+        <v>18</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -724,7 +742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -738,7 +756,7 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
         <v>20</v>
@@ -746,21 +764,16 @@
       <c r="I3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D4" t="s">
-        <v>16</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
       </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -774,236 +787,236 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AMJ12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.5703125" style="2"/>
-    <col min="3" max="3" width="40.7109375" style="2" customWidth="1"/>
-    <col min="4" max="6" width="11.5703125" style="2"/>
-    <col min="7" max="7" width="29.5703125" style="2" customWidth="1"/>
-    <col min="8" max="1024" width="11.5703125" style="2"/>
+    <col min="1" max="2" width="11.5703125" style="1"/>
+    <col min="3" max="3" width="40.7109375" style="1" customWidth="1"/>
+    <col min="4" max="6" width="11.5703125" style="1"/>
+    <col min="7" max="7" width="29.5703125" style="1" customWidth="1"/>
+    <col min="8" max="1024" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>71</v>
+    </row>
+    <row r="12" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1019,253 +1032,253 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AMJ13"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.5703125" style="2"/>
-    <col min="3" max="3" width="28.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="11.5703125" style="2"/>
-    <col min="7" max="7" width="38.85546875" style="2" customWidth="1"/>
-    <col min="8" max="1024" width="11.5703125" style="2"/>
+    <col min="1" max="2" width="11.5703125" style="1"/>
+    <col min="3" max="3" width="28.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="11.5703125" style="1"/>
+    <col min="7" max="7" width="38.85546875" style="1" customWidth="1"/>
+    <col min="8" max="1024" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="D10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    </row>
+    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>76</v>
+      <c r="K13" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1281,7 +1294,140 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -1292,49 +1438,49 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="B3" t="s">
-        <v>83</v>
-      </c>
       <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1343,78 +1489,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -1423,51 +1501,63 @@
     <col min="5" max="5" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
         <v>77</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1476,10 +1566,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -1488,49 +1578,49 @@
     <col min="5" max="5" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
         <v>77</v>
       </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
